--- a/samples/system_ibt_500_ingest.xlsx
+++ b/samples/system_ibt_500_ingest.xlsx
@@ -644,31 +644,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -697,31 +687,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -750,31 +730,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -803,31 +773,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -856,31 +816,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -909,31 +859,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -962,19 +902,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -990,7 +922,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1019,31 +950,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1072,31 +993,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1125,31 +1036,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1178,31 +1079,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1231,31 +1122,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1284,31 +1165,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1337,31 +1208,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1390,31 +1251,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1443,31 +1294,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1496,19 +1337,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1524,7 +1357,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1553,31 +1385,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1606,31 +1428,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1659,31 +1471,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1712,31 +1514,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1765,31 +1557,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1818,31 +1600,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1871,31 +1643,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1924,31 +1686,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1977,31 +1729,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2030,31 +1772,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2083,31 +1815,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2136,19 +1858,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2164,7 +1878,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2193,31 +1906,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2246,19 +1949,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2274,7 +1969,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2303,31 +1997,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2356,19 +2040,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2384,7 +2060,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2413,31 +2088,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2466,19 +2131,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2494,7 +2151,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2523,31 +2179,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2576,31 +2222,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2629,19 +2265,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2657,7 +2285,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2686,19 +2313,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2714,7 +2333,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2743,19 +2361,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2771,7 +2381,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2800,31 +2409,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2853,19 +2452,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2881,7 +2472,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2910,31 +2500,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2963,19 +2543,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2991,7 +2563,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3020,19 +2591,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3048,7 +2611,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3077,19 +2639,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3105,7 +2659,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3134,19 +2687,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3162,7 +2707,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3191,19 +2735,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3219,7 +2755,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3248,19 +2783,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3276,7 +2803,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3305,31 +2831,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3358,19 +2874,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3386,7 +2894,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3415,19 +2922,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3443,7 +2942,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3472,19 +2970,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3500,7 +2990,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3529,19 +3018,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3557,7 +3038,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3586,31 +3066,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3639,19 +3109,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3667,7 +3129,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3696,19 +3157,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3724,7 +3177,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3753,19 +3205,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3781,7 +3225,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3810,19 +3253,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3838,7 +3273,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3867,19 +3301,11 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3895,7 +3321,6 @@
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3924,31 +3349,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3977,31 +3392,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4030,31 +3435,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4083,31 +3478,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4214,7 +3599,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Jawa 7 - GITET Balaraja</t>
@@ -4235,7 +3619,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -4249,8 +3632,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4267,13 +3648,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Jawa 7 - GITET Lontar Baru (LBE)</t>
@@ -4294,7 +3673,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -4308,8 +3686,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4326,13 +3702,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Suralaya - GITET Suralaya Baru</t>
@@ -4353,7 +3727,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -4367,8 +3740,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4385,13 +3756,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Suralaya Baru - GITET Lontar Baru (LBE)</t>
@@ -4412,7 +3781,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -4426,8 +3794,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4444,13 +3810,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Suralaya - GITET Balaraja</t>
@@ -4471,7 +3835,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -4485,8 +3848,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4503,13 +3864,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Suralaya - GITET Cilegon</t>
@@ -4530,7 +3889,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -4544,8 +3902,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4562,13 +3918,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Jawa 9,10 - GITET Cilegon</t>
@@ -4589,7 +3943,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -4603,8 +3956,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4621,13 +3972,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Balaraja - GITET Lengkong</t>
@@ -4648,7 +3997,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -4662,8 +4010,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4680,13 +4026,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Lontar Baru (LBE) - GITET Balaraja</t>
@@ -4707,7 +4051,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -4721,8 +4064,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4739,13 +4080,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Cilegon - GITET Cibinong</t>
@@ -4766,7 +4105,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -4780,8 +4118,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4798,13 +4134,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Gandul - GITET Depok</t>
@@ -4825,7 +4159,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -4839,8 +4172,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4857,13 +4188,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Depok - GITET Cibinong</t>
@@ -4884,7 +4213,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -4898,8 +4226,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4916,13 +4242,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Lengkong - GITET Gandul</t>
@@ -4943,7 +4267,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -4957,8 +4280,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -4975,13 +4296,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kembangan - GITET Gandul</t>
@@ -5002,7 +4321,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -5016,8 +4334,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5034,13 +4350,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Gandul - GITET Durikosambi</t>
@@ -5061,7 +4375,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -5075,8 +4388,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5093,13 +4404,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kembangan - GITET Durikosambi</t>
@@ -5120,7 +4429,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -5134,8 +4442,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5152,13 +4458,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Durikosambi - GITET Muara Karang</t>
@@ -5179,7 +4483,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -5193,8 +4496,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5211,13 +4512,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Muara Tawar - GITET Cawang</t>
@@ -5238,7 +4537,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -5252,8 +4550,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5270,13 +4566,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Muara Tawar - GITET Tambun</t>
@@ -5297,7 +4591,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -5311,8 +4604,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5329,13 +4620,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Tambun - GITET Bekasi</t>
@@ -5356,7 +4645,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -5370,8 +4658,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5388,13 +4674,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Bekasi - GITET Muara Tawar</t>
@@ -5415,7 +4699,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -5429,8 +4712,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5447,13 +4728,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Muara Tawar - GITET Priok</t>
@@ -5474,7 +4753,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -5488,8 +4766,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5506,13 +4782,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Priok - GITET Muara Karang</t>
@@ -5533,7 +4807,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -5547,8 +4820,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5565,13 +4836,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Cawang - GITET Gandul</t>
@@ -5592,7 +4861,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -5606,8 +4874,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5624,13 +4890,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Sukatani - GITET Cilamaya</t>
@@ -5651,7 +4915,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -5665,8 +4928,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5683,13 +4944,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Sukatani - GITET Cibatu</t>
@@ -5710,7 +4969,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -5724,8 +4982,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5742,13 +4998,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Deltamas - GITET Cibatu</t>
@@ -5769,7 +5023,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -5783,8 +5036,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5801,13 +5052,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Cirata - GITET Sukatani</t>
@@ -5828,7 +5077,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -5842,8 +5090,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5860,13 +5106,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Saguling - GITET Bandung Selatan</t>
@@ -5887,7 +5131,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -5901,8 +5144,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5919,13 +5160,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Bandung Selatan - GITET Ujungberung</t>
@@ -5946,7 +5185,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -5960,8 +5198,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -5978,13 +5214,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Mandirancan - GITET Ujungberung</t>
@@ -6005,7 +5239,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -6019,8 +5252,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6037,13 +5268,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Mandirancan - GITET Bandung Selatan</t>
@@ -6064,7 +5293,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -6078,8 +5306,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6096,13 +5322,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Cibinong - GITET Indramayu</t>
@@ -6123,7 +5347,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -6137,8 +5360,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6155,13 +5376,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Indramayu - GITET Mandirancan</t>
@@ -6182,7 +5401,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -6196,8 +5414,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6214,13 +5430,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Tasikmalaya - GITET Bandung Selatan</t>
@@ -6241,7 +5455,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -6255,8 +5468,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6273,13 +5484,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Tasikmalaya - GITET Depok</t>
@@ -6300,7 +5509,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -6314,8 +5522,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6332,13 +5538,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kesugihan - GITET Tasikmalaya</t>
@@ -6359,7 +5563,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -6373,8 +5576,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6391,13 +5592,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kesugihan - GITET Adipala</t>
@@ -6418,7 +5617,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -6432,8 +5630,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6450,13 +5646,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Adipala - GITET Cilacap</t>
@@ -6477,7 +5671,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -6491,8 +5684,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6509,13 +5700,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Pemalang - GITET Batang</t>
@@ -6536,7 +5725,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -6550,8 +5738,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6568,13 +5754,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Pemalang - GITET New Tanjung Jati</t>
@@ -6595,7 +5779,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -6609,8 +5792,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6627,13 +5808,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET New Tanjung Jati - GITET Ungaran</t>
@@ -6654,7 +5833,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -6668,8 +5846,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6686,13 +5862,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Tanjung Jati B - GITET Ungaran</t>
@@ -6713,7 +5887,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -6727,8 +5900,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6745,13 +5916,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kesugihan - GITET Mandirancan</t>
@@ -6772,7 +5941,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -6786,8 +5954,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6804,13 +5970,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kesugihan - GITET Pemalang</t>
@@ -6831,7 +5995,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -6845,8 +6008,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6863,13 +6024,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Ungaran - GITET Boyolali</t>
@@ -6890,7 +6049,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>1</v>
       </c>
@@ -6904,8 +6062,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6922,13 +6078,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Boyolali - GITET Pedan</t>
@@ -6949,7 +6103,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -6963,8 +6116,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -6981,13 +6132,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Ungaran - GITET Krian</t>
@@ -7008,7 +6157,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -7022,8 +6170,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7040,13 +6186,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Ungaran - GITET Ngimbang</t>
@@ -7067,7 +6211,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -7081,8 +6224,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7099,13 +6240,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Paiton - GITET Grati</t>
@@ -7126,7 +6265,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -7140,8 +6278,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7158,13 +6294,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Grati - GITET Krian</t>
@@ -7185,7 +6319,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -7199,8 +6332,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7217,13 +6348,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Paiton - GITET Kediri</t>
@@ -7244,7 +6373,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>2</v>
       </c>
@@ -7258,8 +6386,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7276,13 +6402,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Kediri - GITET Pedan</t>
@@ -7303,7 +6427,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -7317,8 +6440,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7335,13 +6456,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Krian - GITET Gresik</t>
@@ -7362,7 +6481,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>2</v>
       </c>
@@ -7376,8 +6494,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7394,13 +6510,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>SUTET 500 kV GITET Krian - GITET Ngimbang</t>
@@ -7421,7 +6535,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -7435,8 +6548,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7453,13 +6564,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Jawa 7 - GITET Jawa 7</t>
@@ -7480,7 +6589,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>2</v>
       </c>
@@ -7494,8 +6602,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7512,13 +6618,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Lontar Baru (LBE) - GITET Lontar Baru (LBE)</t>
@@ -7539,7 +6643,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -7553,8 +6656,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7571,13 +6672,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Suralaya Baru - GITET Suralaya Baru</t>
@@ -7598,7 +6697,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -7612,8 +6710,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7630,13 +6726,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Suralaya - GITET Suralaya</t>
@@ -7657,7 +6751,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>2</v>
       </c>
@@ -7671,8 +6764,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7689,13 +6780,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Jawa 9,10 - GITET Jawa 9,10</t>
@@ -7716,7 +6805,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>2</v>
       </c>
@@ -7730,8 +6818,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7748,13 +6834,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Priok - GITET Priok</t>
@@ -7775,7 +6859,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>2</v>
       </c>
@@ -7789,8 +6872,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7807,13 +6888,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Muara Tawar - GITET Muara Tawar</t>
@@ -7834,7 +6913,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -7848,8 +6926,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7866,13 +6942,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Cilamaya - GITET Cilamaya</t>
@@ -7893,7 +6967,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>2</v>
       </c>
@@ -7907,8 +6980,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7925,13 +6996,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Cirata - GITET Cirata</t>
@@ -7952,7 +7021,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -7966,8 +7034,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -7984,13 +7050,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Saguling - GITET Saguling</t>
@@ -8011,7 +7075,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -8025,8 +7088,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8043,13 +7104,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Adipala - GITET Adipala</t>
@@ -8070,7 +7129,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>2</v>
       </c>
@@ -8084,8 +7142,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8102,13 +7158,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Cilacap - GITET Cilacap</t>
@@ -8129,7 +7183,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -8143,8 +7196,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8161,13 +7212,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Batang - GITET Batang</t>
@@ -8188,7 +7237,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>2</v>
       </c>
@@ -8202,8 +7250,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8220,13 +7266,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit New Tanjung Jati - GITET New Tanjung Jati</t>
@@ -8247,7 +7291,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -8261,8 +7304,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8279,13 +7320,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Tanjung Jati B - GITET Tanjung Jati B</t>
@@ -8306,7 +7345,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>2</v>
       </c>
@@ -8320,8 +7358,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8338,13 +7374,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Gresik - GITET Gresik</t>
@@ -8365,7 +7399,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>2</v>
       </c>
@@ -8379,8 +7412,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8397,13 +7428,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Grati - GITET Grati</t>
@@ -8424,7 +7453,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>2</v>
       </c>
@@ -8438,8 +7466,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8456,13 +7482,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>SUTET 500 kV Pembangkit Paiton - GITET Paiton</t>
@@ -8483,7 +7507,6 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>2</v>
       </c>
@@ -8497,8 +7520,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Jawa-Madura-Bali</t>
@@ -8515,7 +7536,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8625,7 +7645,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -8669,7 +7688,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8708,8 +7726,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -8753,7 +7769,6 @@
           <t>28;29</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8797,7 +7812,6 @@
           <t>10;11</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8836,8 +7850,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8881,7 +7893,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8925,7 +7936,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8969,7 +7979,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9008,8 +8017,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9048,8 +8055,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9093,7 +8098,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9132,8 +8136,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9177,7 +8179,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9221,7 +8222,6 @@
           <t>30;31</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9265,7 +8265,6 @@
           <t>34;35</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9309,7 +8308,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9353,7 +8351,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9397,7 +8394,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9436,8 +8432,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9481,7 +8475,6 @@
           <t>7;8</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9520,8 +8513,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9560,8 +8551,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -9605,7 +8594,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -9649,7 +8637,6 @@
           <t>23;24;25</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -9693,7 +8680,6 @@
           <t>37;38</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -9737,7 +8723,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -9776,8 +8761,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -9821,7 +8804,6 @@
           <t>1;2</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -9865,7 +8847,6 @@
           <t>17;18;19;20</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -9909,7 +8890,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -9953,7 +8933,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -9997,7 +8976,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -10041,7 +9019,6 @@
           <t>21;22</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10115,17 +9092,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.Pemeliharaan IBT sulit dilakukan. 2.Pertumbuhan beban menjadi terhambat. 3.Terjadi pemadaman apabila trip salah satu IBT di Suralaya</t>
+          <t>1. Pemeliharaan IBT sulit dilakukan. 2. Pertumbuhan beban menjadi terhambat. 3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025). 2.Rencana penambahan target DS OLS SSSuralaya 1,2dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025). 3.Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit-3 beroperasi</t>
+          <t>1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025). 2. Rencana penambahan target DS OLS SSSuralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025). 3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit-3 beroperasi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Uprating IBT-1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 - 2034, COD di Tahun 2026</t>
+          <t>Jangka Pendek : Uprating IBT-1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 - 2034, COD di Tahun 2026</t>
         </is>
       </c>
     </row>
@@ -10155,12 +9132,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025). 2.Rencana penambahan target DS OLS SSSuralaya 1,2dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025). 3.Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit-3 beroperasi</t>
+          <t>1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025). 2. Rencana penambahan target DS OLS SSSuralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025). 3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit-3 beroperasi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Uprating IBT-1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 - 2034, COD di Tahun 2026</t>
+          <t>Jangka Pendek : Uprating IBT-1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 - 2034, COD di Tahun 2026</t>
         </is>
       </c>
     </row>
@@ -10185,17 +9162,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.PemeliharaanIBT sulitdilakukan. 2.Terjadi pemdaman apabila trip salah satu IBT di Cilegon</t>
+          <t>1. PemeliharaanIBT sulit dilakukan. 2. Terjadi pemdaman apabila trip salah satu IBT di Cilegon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Pemindahanbeban GICikande&amp; GI BalarajakeSubsiste mBalaraja 1&amp;2- Lontar- Kembangan1,2. 2.Pemindahan beban Trafo-1 GI Cilegon Baru, KTT Posco dan KTT KSTEL ke Sub Sistem Suralaya Mitigasi Unit 3-Suralaya 1,2-Cilegon 4 3.Pemindahaan beban GI Saketi dan Malimping ke Subsistem Pelabuhan Ratu. 4.Telah dipasang OLS IBT Cilegon tahap 1 sd 4 dengan total target 614 MW. (Berdasarkan Buku defence scheme Tahun 2025) 5.Rencana penambahan target DS OLS IBT Cilegondengan total target sebesar 666 MW (Berdasarkan buku DS Tahun 2025). 6.Usulan pengoperasian 2 GT PLTGU Cilegon</t>
+          <t>1.Pemindahan beban GI Cikande&amp; GI Balaraja ke Subsiste mBalaraja 1&amp;2- Lontar- Kembangan 1,2. 2. Pemindahan beban Trafo-1 GI Cilegon Baru, KTT Posco dan KTT KSTEL ke Sub Sistem Suralaya Mitigasi Unit 3-Suralaya 1,2-Cilegon 4 3. Pemindahaan beban GI Saketi dan Malimping ke Subsistem Pelabuhan Ratu. 4. Telah dipasang OLS IBT Cilegon tahap 1 sd 4 dengan total target 614 MW. (Berdasarkan Buku defence scheme Tahun 2025) 5. Rencana penambahan target DS OLS IBT Cilegon dengan total target sebesar 666 MW (Berdasarkan buku DS Tahun 2025). 6. Usulan pengoperasian 2 GT PLTGU Cilegon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan GITETCikande berikut outlet,sesuaiRUPTL 2025 - 2034 COD Tahun2026. COD timeline proyek tahun 2027 (Progres proyek , GITET : sudah konstruksi, Line Bay : pengadaan). Usulan / Solusi Jangka Menengah : 2.Usulan Pembangunan IBT-1 &amp; 2 di GITET Jawa 7 beserta outletnya (diusulkan COD 2029). Jangka Menengah: 3.Usulan Pembangunan BESS tersebar di GI 150 kV Cilegon dan GI 150 kV Menes masing- masing 100 MW</t>
+          <t>Jangka Pendek : 1. Pembangunan GITETCikande berikut outlet, sesuaiRUPTL 2025 - 2034 COD Tahun 2026. COD timeline proyek tahun 2027 (Progres proyek , GITET : sudah konstruksi, Line Bay : pengadaan). Usulan / Solusi Jangka Menengah : 2. Usulan Pembangunan IBT-1 &amp; 2 di GITET Jawa 7 beserta outletnya (diusulkan COD 2029). Jangka Menengah : 3. Usulan Pembangunan BESS tersebar di GI 150 kV Cilegon dan GI 150 kV Menes masing- masing 100 MW</t>
         </is>
       </c>
     </row>
@@ -10225,12 +9202,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Kembangan tahap 1 sd 4 sebesar 908 MW (Berdasarkan buku DS Tahun 2025). 2.Rencana penambahan target OLS IBT Kembangan tahap 1 sd 4 total sebesar 1207 MW. (Berdasarkan buku DS Tahun 2025). 3.Pekerjaan bisa dilaksanakan pada saat beban pembangkitan Lontar 4 unit Maksimum atau saat beban rendah. 4.Pengalihan beban ke sub sistem Muarakarang atau Gandul 1,3- Durikosambi 2</t>
+          <t>1. Sudah terpasang OLS IBT Kembangan tahap 1 sd 4 sebesar 908 MW (Berdasarkan buku DS Tahun 2025). 2. Rencana penambahan target OLS IBT Kembangan tahap 1 sd 4 total sebesar 1207 MW. (Berdasarkan buku DS Tahun 2025). 3. Pekerjaan bisa dilaksanakan pada saat beban pembangkitan Lontar 4 unit Maksimum atau saat beban rendah. 4. Pengalihan beban ke sub sistem Muarakarang atau Gandul 1,3- Durikosambi 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan GITET Cikupa dan 2 unit IBT 500/150 kV serta outlet terkait untuk mengambil beban GI Cikupa, GI Jatake Baru, GI Maxim dan GI Tangerang lama (RUPTL 2025 - 2034, COD 2025). COD timeline proyekDesember 2027, menunggu outletnya. 2.Pembangunan 2 Unit IBT 500/150 kV Ext IBT 3,4 Durikosambi. (RUPTL 2025 - 2034, COD 2027). 3.Pembangunan PLTSA Tangerang dengan kapasitas 45 MW (RUPTL 2025 - 2034, COD Tahun 2028). Jangka Panjang : 4.Usulan Pembangunan BESS tersebar di GI 150 kV Cikupa dan GI 150 kV Teluknaga masing- Usulan / Solusi masing 100 MW. (RUPTL 2025 - 2034) COD Tahun 2032</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET Cikupa dan 2 unit IBT 500/150 kV serta outlet terkait untuk mengambil beban GI Cikupa, GI Jatake Baru, GI Maxim dan GI Tangerang lama (RUPTL 2025 - 2034, COD 2025). COD timeline proyek Desember 2027, menunggu outletnya. 2. Pembangunan 2 Unit IBT 500/150 kV Ext IBT 3,4 Durikosambi. (RUPTL 2025 - 2034, COD 2027). 3. Pembangunan PLTSA Tangerang dengan kapasitas 45 MW (RUPTL 2025 - 2034, COD Tahun 2028). Jangka Panjang : 4. Usulan Pembangunan BESS tersebar di GI 150 kV Cikupa dan GI 150 kV Teluknaga masing- Usulan / Solusi masing 100 MW. (RUPTL 2025 - 2034) COD Tahun 2032</t>
         </is>
       </c>
     </row>
@@ -10260,12 +9237,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.Penjadwalan pemeliharaan dilakukan pada periode beban rendah. 2.Looping dengan Sub Sistem Muarakarang saat terdapat pekerjaan IBT di Sub sistem terkait. 3.Telah terpasang skema OLS pada IBT-2,3 Cawang- Depok 1 tahap 1-4 dengan total target sebesar 294 MW (berdasarkan buku DS Tahun 2025). 4.Rencana penambahan skema OLS pada OLS IBT-2,3 Cawang-Depok 1 dengan total target 388 MW (berdasarkan buku DS Tahun 2025)</t>
+          <t>1. Penjadwalan pemeliharaan dilakukan pada periode beban rendah. 2. Looping dengan Sub Sistem Muarakarang saat terdapat pekerjaan IBT di Sub sistem terkait. 3. Telah terpasang skema OLS pada IBT-2,3 Cawang- Depok 1 tahap 1-4 dengan total target sebesar 294 MW (berdasarkan buku DS Tahun 2025). 4. Rencana penambahan skema OLS pada OLS IBT-2,3 Cawang-Depok 1 dengan total target 388 MW (berdasarkan buku DS Tahun 2025)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Percepatan pembangunan Proyek Uprating SUTT/SKTT ex-70 kV ke SUTT/SKTT 150 kV Ragunan- Cawang Baru. (RUPTL 2025 - 2034, COD 2026). 2.Pembangunaan GITET Citereup beserta outlet. (RUPTL 2025 - 2034 COD 2028)</t>
+          <t>Jangka Pendek : 1. Percepatan pembangunan Proyek Uprating SUTT/SKTT ex-70 kV ke SUTT/SKTT 150 kV Ragunan- Cawang Baru. (RUPTL 2025 - 2034, COD 2026). 2.Pembangunaan GITET Citereup beserta outlet. (RUPTL 2025 - 2034 COD 2028)</t>
         </is>
       </c>
     </row>
@@ -10295,12 +9272,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.Beban GI Pondok Kelapa dipasok SS Tambun 1,2 (UP2B Jawa Barat). 2.Beban GIS Gandaria dipasok SS Cibinong 1,2-Depok 2-Salak- Pratu selama pekerjaan IBT. 3.Looping dengan IBT 1,2 Tambun selama pekerjaan IBT pada sub sistem tersebut. 4.Telah dipasang OLS tahap 1 sd 3 total target 299 MW sesuai buku DS Tahun 2025. 5.Rencana penambahan target OLS tahap 1 sd 3 Mitigasi total target 382 MW sesuai buku DS Tahun 2025</t>
+          <t>1. Beban GI Pondok Kelapa dipasok SS Tambun 1,2 (UP2B Jawa Barat). 2. Beban GIS Gandaria dipasok SS Cibinong 1,2-Depok 2-Salak- Pratu selama pekerjaan IBT. 3. Looping dengan IBT 1,2 Tambun selama pekerjaan IBT pada sub sistem tersebut. 4. Telah dipasang OLS tahap 1 sd 3 total target 299 MW sesuai buku DS Tahun 2025. 5. Rencana penambahan target OLS tahap 1 sd 3 Mitigasi total target 382 MW sesuai buku DS Tahun 2025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.Usulan pengaktifan kembali SUTT 150 kV Bekasi-New Sukatani (diusulkan COD Tahun 2026). Jangka Menengah: 2.Usulan Penambahan IBT-4 Cibinong COD Tahun 2029. 3.Usulan Pembangunan GITET Jatirangon COD Tahun 2029</t>
+          <t>Jangka Pendek: 1. Usulan pengaktifan kembali SUTT 150 kV Bekasi-New Sukatani (diusulkan COD Tahun 2026). Jangka Menengah : 2. Usulan Penambahan IBT-4 Cibinong COD Tahun 2029. 3. Usulan Pembangunan GITET Jatirangon COD Tahun 2029</t>
         </is>
       </c>
     </row>
@@ -10325,17 +9302,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Potensi padam sebesar 239 MW jika terjadi trip 1 IBT pada GITET Cibatu 3,4 (N-1). 2.Potensi padam sebesar 1039 MW bila trip 2 IBT (N- 2) Beban SS Cibatu 3,4. 3.Drop tegangan di Subsistem Cibatu 3,4 bila trip 1 IBT</t>
+          <t>1. Potensi padam sebesar 239 MW jika terjadi trip 1 IBT pada GITET Cibatu 3,4 (N-1). 2. Potensi padam sebesar 1039 MW bila trip 2 IBT (N- 2) Beban SS Cibatu 3,4. 3. Drop tegangan di Subsistem Cibatu 3,4 bila trip 1 IBT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.Telah Terpasang Skema OLS IBT 3,4 Cibatu tahap 1-2-3 dengan total target sebesar541MW. 2.Sudah terpasang ADS Indramayu sisi Barat jika terjadi kontingensi N-2 pada IBT Cibatu 3,4 (Progresterakhirda ri hasil uji PUSERTIF, perlu implementasi kontingensi ADS sisi Timur) 3.Pekerjaan pemeliharaaan dilakukan saat beban rendah. 4.Rekonfigurasi jaringan untuk alih beban</t>
+          <t>1. Telah Terpasang Skema OLS IBT 3,4 Cibatu tahap 1-2-3 dengan total target sebesar 541MW. 2. Sudah terpasang ADS Indramayu sisi Barat jika terjadi kontingensi N-2 pada IBT Cibatu 3,4 (Progresterakhirda ri hasil uji PUSERTIF, perlu implementasi kontingensi ADS sisi Timur) 3. Pekerjaan pemeliharaaan dilakukan saat beban rendah. 4. Rekonfigurasi jaringan untuk alih beban</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani Gobel). Sesuai RUPTL 2025 - 2034 COD 2025. Update : Pemadaman Tahap-1 dilaksanakan mulai 19 Agustus 2025 s.d 19 Nov 2025 2.Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 - 2034 COD 2025. Update : Proses Pengadaan. 3.Pembangunan GITET Karawang dan outlet terkait. Sesuai RUPTL 2025-2034 COD tahun 2027</t>
+          <t>Jangka Pendek : 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani Gobel). Sesuai RUPTL 2025 - 2034 COD 2025. Update : Pemadaman Tahap-1 dilaksanakan mulai 19 Agustus 2025 s.d 19 Nov 2025 2. Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 - 2034 COD 2025. Update : Proses Pengadaan. 3. Pembangunan GITET Karawang dan outlet terkait. Sesuai RUPTL 2025-2034 COD tahun 2027</t>
         </is>
       </c>
     </row>
@@ -10360,17 +9337,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam398 MW apabila trip 1 IBT (N-1). 2.Berpotensi padam760MW apabila trip 2 IBT (N-2). 3.Fleksibilitas operasi dan keandalan menjadi berkurang</t>
+          <t>1. Berpotensi padam 398 MW apabila trip 1 IBT (N-1). 2. Berpotensi padam 760MW apabila trip 2 IBT (N-2). 3. Fleksibilitas operasi dan keandalan menjadi berkurang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,2 GITET Mandirancan tahap 1-2-3 dengan total target 398MW. 2.Pekerjaan pemeliharaaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT 1,2 GITET Mandirancan tahap 1-2-3 dengan total target 398 MW. 2. Pekerjaan pemeliharaaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 - 2034 COD 2025. Update Proses Pengadaan. 2.Pembangunan GITET Karawang dan outlet terkait. Sesuai RUPTL 2025-2034 COD tahun 2027</t>
+          <t>Jangka Pendek : 1.Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 - 2034 COD 2025. Update Proses Pengadaan. 2.Pembangunan GITET Karawang dan outlet terkait. Sesuai RUPTL 2025-2034 COD tahun 2027</t>
         </is>
       </c>
     </row>
@@ -10395,17 +9372,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.Terjadi overload di IBT-1 atau 2 Cirata. 2.Berpotensi padam850 MW apabila trip 2 IBT (N-2 IBT GITET Cirata). 3.Fleksibilitas operasi dan keandalan menjadi berkurang. 4.Dapat menyebabkan kerusakan peralatan jika SCL terlalu besar</t>
+          <t>1. Terjadi overload di IBT-1 atau 2 Cirata. 2. Berpotensi padam 850 MW apabila trip 2 IBT (N-2 IBT GITET Cirata). 3. Fleksibilitas operasi dan keandalan menjadi berkurang. 4. Dapat menyebabkan kerusakan peralatan jika SCL terlalu besar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang Skema OLS IBT Cirata 1,2,3 total target sebesar312 MW. 2.Pekerjaan pemeliharaan dilakukan saat beban rendah. 3.Dilakukan pola operasi split IBT ketika diperlukan seluruh unit PLTA Cirata, Saguling dan Jatiluhur beroperasi</t>
+          <t>1. Sudah terpasang Skema OLS IBT Cirata 1,2,3 total target sebesar 312 MW. 2. Pekerjaan pemeliharaan dilakukan saat beban rendah. 3. Dilakukan pola operasi split IBT ketika diperlukan seluruh unit PLTA Cirata, Saguling dan Jatiluhur beroperasi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Usulan pemasangan Fault Current Limiter (FCL) saat looping 3 IBT 500/150 kV di GI Cirata. diusulkan COD Tahun 2026. Jangka Menengah: 2.Pembangunan SUTT 150 kV Pabuaran- Dawuan II/ Megatama Putra Sejahtera. Sesuai RUPTL 2025 - 2034, COD 2031. Proyek ini bertujuan agar dapat looping jauh dengan IBT 1,2 di GITET Mandirancan.Terdapat perubahan dengan adanya Kawasan Subang Smartpolitan dan BYD dengan Konfigurasi GI Pabuaran - GI Subang Smartpolitan - GI Subang Baru Inc. SUTT Sukamandi-Haurgeulis. 3.Pembangunan IBT-5,6 GITET Karawang. Sesuai RUPTL 2025-2034 COD tahun 2028</t>
+          <t>Jangka Pendek : 1. Usulan pemasangan Fault Current Limiter (FCL) saat looping 3 IBT 500/150 kV di GI Cirata. diusulkan COD Tahun 2026. Jangka Menengah : 2.Pembangunan SUTT 150 kV Pabuaran- Dawuan II/ Megatama Putra Sejahtera. Sesuai RUPTL 2025 - 2034, COD 2031. Proyek ini bertujuan agar dapat looping jauh dengan IBT 1,2 di GITET Mandirancan. Terdapat perubahan dengan adanya Kawasan Subang Smartpolitan dan BYD dengan Konfigurasi GI Pabuaran - GI Subang Smartpolitan - GI Subang Baru Inc. SUTT Sukamandi-Haurgeulis. 3.Pembangunan IBT-5,6 GITET Karawang. Sesuai RUPTL 2025-2034 COD tahun 2028</t>
         </is>
       </c>
     </row>
@@ -10430,17 +9407,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.Berpotensi Padam sekitar541 MW apabila terjadi trip 2 IBT (Kondisi N-2). 2.Fleksibilitas operasi dan keandalan berkurang</t>
+          <t>1. Berpotensi Padam sekitar 541 MW apabila terjadi trip 2 IBT (Kondisi N-2). 2. Fleksibilitas operasi dan keandalan berkurang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.Telah Terpasang OLS IBT 1,2 Cibatu dengan total target 229MW. 2.Pekerjaan pemeliharaaan dilakukan saat beban rendah. 3.Rekonfigurasi jaringan di GI 150 kV Cibatu. 4.Rekonfigurasi jaringan di GI 150 kV Gandamekar</t>
+          <t>1. Telah Terpasang OLS IBT 1,2 Cibatu dengan total target 229 MW. 2. Pekerjaan pemeliharaaan dilakukan saat beban rendah. 3. Rekonfigurasi jaringan di GI 150 kV Cibatu. 4. Rekonfigurasi jaringan di GI 150 kV Gandamekar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025. 2.Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani - Fajar SW, RUPTL 2025 - 2034, COD Tahun 2027</t>
+          <t>Jangka Pendek : 1.Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025. 2.Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani - Fajar SW, RUPTL 2025 - 2034, COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -10465,17 +9442,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.Berpotensi Padam sekitar372 MW jika terjadi trip 2 IBT (N-2) (asumsi beban saat loop 4 IBT). 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan IBT</t>
+          <t>1. Berpotensi Padam sekitar 372 MW jika terjadi trip 2 IBT (N-2) (asumsi beban saat loop 4 IBT). 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.Telah Terpasang OLS IBT 3,4Deltamas (Ketika pasokan hingga GI PLTU Indramayu/looping dengan Subsistem Mandirancan) Total target359 MW. 2.Rekonfigurasi di GI 150 kV pinayungan apabila ada pemeliharaan 1 IBT di GITET Deltamas yang dilaksanakan pada saat beban rendah/ hari libur</t>
+          <t>1. Telah Terpasang OLS IBT 3,4 Deltamas (Ketika pasokan hingga GI PLTU Indramayu/looping dengan Subsistem Mandirancan) Total target 359 MW. 2. Rekonfigurasi di GI 150 kV pinayungan apabila ada pemeliharaan 1 IBT di GITET Deltamas yang dilaksanakan pada saat beban rendah/ hari libur</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025-2034 COD 2025. Update Pemadaman Tahap-1 dilaksanakan mulai 19 Agustus 2025 s.d 19 Nov 2025. 2.Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025</t>
+          <t>Jangka Pendek : 1.Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025 -2034 COD 2025. Update Pemadaman Tahap-1 dilaksanakan mulai 19 Agustus 2025 s.d 19 Nov 2025. 2.Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025</t>
         </is>
       </c>
     </row>
@@ -10500,17 +9477,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.Berpotensi Padam sekitar302 MW jika terjadi trip 2 IBT (N-2). 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan IBT</t>
+          <t>1. Berpotensi Padam sekitar 302 MW jika terjadi trip 2 IBT (N-2). 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.Telah Terpasang OLS IBT 1,2 Deltamas (Ketika pasokan hingga GI PLTU Indramayu/looping dengan Subsistem Mandirancan) Total target 291 MW. 2.Pengembangan OLS Aktif saat dengan SS CBATU 1,2 dan penambahan target dengan mempertimbangka n kontingensi N-1/ N-2 IBT Cibatu dengan total target 335 MW. 3.Rekonfigurasi di GI 150 kV pinayungan apabila ada pemeliharaan 1 IBT di GITET Deltamas yang dilaksanakan Mitigasi pada saat beban rendah/ hari libur</t>
+          <t>1. Telah Terpasang OLS IBT 1,2 Deltamas (Ketika pasokan hingga GI PLTU Indramayu/looping dengan Subsistem Mandirancan) Total target 291 MW. 2. Pengembangan OLS Aktif saat dengan SS CBATU 1,2 dan penambahan target dengan mempertimbangka n kontingensi N-1/ N-2 IBT Cibatu dengan total target 335 MW. 3. Rekonfigurasi di GI 150 kV pinayungan apabila ada pemeliharaan 1 IBT di GITET Deltamas yang dilaksanakan Mitigasi pada saat beban rendah/ hari libur</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan GITET Karawang (4x500 MVA) dan outletnya (SUTT Karawang-Margakarya), RUPTL 2025 -2034, COD 2027</t>
+          <t>Jangka Pendek : Pembangunan GITET Karawang (4x500 MVA) dan outletnya (SUTT Karawang -Margakarya), RUPTL 2025 - 2034, COD 2027</t>
         </is>
       </c>
     </row>
@@ -10535,17 +9512,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.Potensi padam sebesar295 MWapabila trip 1 IBT. 2.Berpotensi padam bila terjadi gangguan N-2 IBT sebesar848 MW. 3.Fleksibilitasi operasi dan keandalan berkurang. 4.Kesulitan bila dilakukan pemeliharaan IBT</t>
+          <t>1. Potensi padam sebesar 295 MW apabila trip 1 IBT. 2. Berpotensi padam bila terjadi gangguan N-2 IBT sebesar 848 MW. 3. Fleksibilitasi operasi dan keandalan berkurang. 4. Kesulitan bila dilakukan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.Telah terpasang OLS IBT 1,2 tahap 1-2 total target sebesar 295 MW. 2.Pemeliharaan IBT dilakukan pada saat beban rendah. 3.Rekonfigurasi jaringan di GI 150 kV Bandung Utara, Ujung Berung. Cigereleng dan Lagadar saat pelaksanaan pemeliharaan IBT</t>
+          <t>1. Telah terpasang OLS IBT 1,2 tahap 1-2 total target sebesar 295 MW. 2. Pemeliharaan IBT dilakukan pada saat beban rendah. 3. Rekonfigurasi jaringan di GI 150 kV Bandung Utara, Ujung Berung. Cigereleng dan Lagadar saat pelaksanaan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JangkaMenengah: 1.Pembangunan GITET Cikalong (IBT dan outlet) Sesuai RUPTL 2025-2034, COD 2027. Jangka Panjang : 2.Pembangunan SUTT 150 kV Jawa Barat Landing Point (BDSLN- WYNDU-KMJNG- DRJAT). Sesuai RUPTL 2025 - 2034, COD bertahap 2026 (BDSLN- WYNDU-KMJNG), 2027 (TSBRU-CAMIS) dan 2029-2030 (KMJNG- DRJAT). Update : sudah masuk TVV namun terdapat potensi revisi menyesuaikan kondisi update di lapangan</t>
+          <t>Jangka Menengah: 1. Pembangunan GITET Cikalong (IBT dan outlet) Sesuai RUPTL 2025 -2034, COD 2027. Jangka Panjang : 2. Pembangunan SUTT 150 kV Jawa Barat Landing Point (BDSLN- WYNDU-KMJNG- DRJAT). Sesuai RUPTL 2025 - 2034, COD bertahap 2026 (BDSLN- WYNDU-KMJNG), 2027 (TSBRU-CAMIS) dan 2029-2030 (KMJNG- DRJAT). Update : sudah masuk TVV namun terdapat potensi revisi menyesuaikan kondisi update di lapangan</t>
         </is>
       </c>
     </row>
@@ -10570,17 +9547,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam bila terjadi gangguan N-2 IBT sebesar809MW. 2.Fleksibilitasi operasi dan keandalan berkurang. 3.Kesulitan bila dilakukan pemeliharaan IBT</t>
+          <t>1. Berpotensi padam bila terjadi gangguan N-2 IBT sebesar 809MW. 2. Fleksibilitasi operasi dan keandalan berkurang. 3. Kesulitan bila dilakukan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.Telah terpasang OLS IBT 1,2 tahap 1-2 total target sebesar183 MW. 2.Pemeliharaan IBT dilakukan pada saat beban rendah. 3.Rekonfigurasi jaringan di GI 150 kV Bandung Utara, Ujung Berung. Cigereleng dan Lagadar saat pelaksanaan pemeliharaan IBT</t>
+          <t>1. Telah terpasang OLS IBT 1,2 tahap 1-2 total target sebesar 183 MW. 2. Pemeliharaan IBT dilakukan pada saat beban rendah. 3. Rekonfigurasi jaringan di GI 150 kV Bandung Utara, Ujung Berung. Cigereleng dan Lagadar saat pelaksanaan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jangka Menengah : 1.Pembangunan GITET Cikalong (IBT dan outlet) Sesuai RUPTL 2025-2034, COD 2027. Jangka Panjang : 2.Pembangunan SUTT 150 kV Jawa Barat Landing Point (BDSLN- WYNDU-KMJNG- DRJAT). Sesuai RUPTL 2025 - 2034, COD bertahap 2026 (BDSLN- WYNDU-KMJNG), 2027 (TSBRU-CAMIS) dan 2029-2030 (KMJNG- DRJAT). Update : sudah masuk TVV namun terdapat potensi revisi menyesuaikan kondisi update di lapangan</t>
+          <t>Jangka Menengah : 1. Pembangunan GITET Cikalong (IBT dan outlet) Sesuai RUPTL 2025 -2034, COD 2027. Jangka Panjang : 2. Pembangunan SUTT 150 kV Jawa Barat Landing Point (BDSLN- WYNDU-KMJNG- DRJAT). Sesuai RUPTL 2025 - 2034, COD bertahap 2026 (BDSLN- WYNDU-KMJNG), 2027 (TSBRU-CAMIS) dan 2029-2030 (KMJNG- DRJAT). Update : sudah masuk TVV namun terdapat potensi revisi menyesuaikan kondisi update di lapangan</t>
         </is>
       </c>
     </row>
@@ -10605,17 +9582,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam bila terjadi gangguan N-2 IBT sebesar484MW. 2.Fleksibilitasi operasi dan keandalan berkurang</t>
+          <t>1. Berpotensi padam bila terjadi gangguan N-2 IBT sebesar 484MW. 2. Fleksibilitasi operasi dan keandalan berkurang</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.Pemeliharaan IBT dilakukan pada saat beban rendah 2.Direncanakan skema OLS IBT 1,2 GITET Tasik tahap 1-2 target PMT Banjar bay Mitigasi Majenang 1,2 (transfer ke UP2B Jawa Tengah dan DIY) pada tahap 1 dan Trafo-2 Banjar di tahap 2 dengan total beban45 MW</t>
+          <t>1. Pemeliharaan IBT dilakukan pada saat beban rendah 2. Direncanakan skema OLS IBT 1,2 GITET Tasik tahap 1-2 target PMT Banjar bay Mitigasi Majenang 1,2 (transfer ke UP2B Jawa Tengah dan DIY) pada tahap 1 dan Trafo-2 Banjar di tahap 2 dengan total beban 45 MW</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan PLTA Wado 50 MW, COD 2029 sesuai RUPTL 2025-2034</t>
+          <t>Jangka Pendek : Pembangunan PLTA Wado 50 MW, COD 2029 sesuai RUPTL 2025-2034</t>
         </is>
       </c>
     </row>
@@ -10640,17 +9617,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.Potensi padam sebesar348 MWapabila trip 1 IBT. 2.Berpotensi Padam sekitar607 MW apabila terjadi gangguan N-2 pada IBT Tambun</t>
+          <t>1. Potensi padam sebesar 348 MW apabila trip 1 IBT. 2. Berpotensi Padam sekitar 607 MW apabila terjadi gangguan N-2 pada IBT Tambun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.Telah terpasang OLS IBT 1,2 Tambun dengan total target348 MW. 2.Rekonfigurasi jaringan looping dengan subsistem Cibatu 1,2</t>
+          <t>1. Telah terpasang OLS IBT 1,2 Tambun dengan total target 348 MW. 2. Rekonfigurasi jaringan looping dengan subsistem Cibatu 1,2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JangkaMenengah: 1.Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025. 2.Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani - Fajar SW, RUPTL 2025 - 2034, COD 2027</t>
+          <t>Jangka Menengah: 1.Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025. 2.Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani - Fajar SW, RUPTL 2025 - 2034, COD 2027</t>
         </is>
       </c>
     </row>
@@ -10675,12 +9652,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Tanjung Jati 1,2 total target sebesar633 MW (Realisasi BP Tahun 2025, 14 Oktober 2025-5.721 MW). 2.Pengoperasian 2 unit PLTU Rembang. 3.Pelaksanaan pemeliharaan pada saat beban rendah/hari libur dengan menurunkan pembebanan Komplek Pembangkitan Tanjung Jati dan mengoperasikan PLTGU Tambaklorok</t>
+          <t>1.Sudah terpasang OLS IBT Tanjung Jati 1,2 total target sebesar 633 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 -5.721 MW). 2.Pengoperasian 2 unit PLTU Rembang. 3.Pelaksanaan pemeliharaan pada saat beban rendah/hari libur dengan menurunkan pembebanan Komplek Pembangkitan Tanjung Jati dan mengoperasikan PLTGU Tambaklorok</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10710,7 +9687,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10745,7 +9722,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan. 4.Terjadi drop tegangan di wilayah Magelang dan Yogyakarta</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan. 4. Terjadi drop tegangan di wilayah Magelang dan Yogyakarta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10755,7 +9732,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora- Purwodadi (RUPTL 2025-2034,COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025-2034,COD 2028). 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi- Sayung(RUPTL 2025- 2034,COD 2028)</t>
+          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora- Purwodadi (RUPTL 2025-2034, COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025-2034, COD 2028). 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi- Sayung (RUPTL 2025- 2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -10780,7 +9757,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.Terjadi drop tegangan di wilayah Magelang dan Yogyakarta jika IBT-3 Ungaran gangguan. 2.Komplain pelanggan KTT SINDO terkait mutu dan pelayanan tegangan saat outage PLTU Rembang 1 Unit. 3.Apabila IBT Ungaran-3 trip berpotensi tejadi kenaikan MVAR di PLTU Rembang sampai 120 MVAR</t>
+          <t>1. Terjadi drop tegangan di wilayah Magelang dan Yogyakarta jika IBT-3 Ungaran gangguan. 2. Komplain pelanggan KTT SINDO terkait mutu dan pelayanan tegangan saat outage PLTU Rembang 1 Unit. 3. Apabila IBT Ungaran-3 trip berpotensi tejadi kenaikan MVAR di PLTU Rembang sampai 120 MVAR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10790,7 +9767,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora- Purwodadi (RUPTL 2025-2034,COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025-2034,COD 2028). 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi- Sayung(RUPTL 2025- 2034,COD 2028)</t>
+          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora- Purwodadi (RUPTL 2025-2034, COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025-2034, COD 2028). 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi- Sayung (RUPTL 2025- 2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -10815,12 +9792,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT (N- 1-1). 2.Berpotensi padam beban sebesar 528 MW saat kondisi N-1- 1. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT (N- 1-1). 2. Berpotensi padam beban sebesar 528 MW saat kondisi N-1- 1. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Sudah terpasang OLS IBT 1,2 Ungaran total target sebesar 528MW(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3.Sudah terpasang skema proteksi island SubsistemUngaran 1,2. 4.Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran(kombinas i) 5.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
+          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Sudah terpasang OLS IBT 1,2 Ungaran total target sebesar 528 MW(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3.Sudah terpasang skema proteksi island Subsistem Ungaran 1,2. 4.Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran (kombinas i) 5.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10850,12 +9827,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT (N- 1-1). 2.Berpotensi padam beban sebesar 528 MW saat kondisi N-1- 1. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT (N- 1-1). 2. Berpotensi padam beban sebesar 528 MW saat kondisi N-1- 1. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Sudah terpasang OLS IBT 1,2,3 Ungaran (Looping) total target sebesar 541MW(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3.Sudah terpasang skema proteksi island SubsistemUngaran 1,2. 4.Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran(kombinas i) 5.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
+          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Sudah terpasang OLS IBT 1,2,3 Ungaran (Looping) total target sebesar 541 MW(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3.Sudah terpasang skema proteksi island Subsistem Ungaran 1,2. 4.Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran (kombinas i) 5.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10885,12 +9862,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload&amp; pemadamansaat gangguan salah satu IBT. 2.Berpotensi padam sebesar 611 MW saat terjadi trip 2 IBT GITET Pedan (N- 2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload &amp; pemadamansaat gangguan salah satu IBT. 2. Berpotensi padam sebesar 611 MW saat terjadi trip 2 IBT GITET Pedan (N- 2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,2 Pedan total target sebesar521 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 2.Memindahkan GI Banyudono ke Subsistem Boyolali. 3.Splitting di GI 150 kV Sragen sehingga sebagian beban GI Sragen dipasok oleh Subsistem Kediri (UP2B Jawa Timur). 4.Pengaturan pemeliharaan saat beban rendah/hari libur dengan looping 3 IBT Pedan Mitigasi serta pengaturan konfigurasi</t>
+          <t>1.Sudah terpasang OLS IBT 1,2 Pedan total target sebesar 521 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 2.Memindahkan GI Banyudono ke Subsistem Boyolali. 3.Splitting di GI 150 kV Sragen sehingga sebagian beban GI Sragen dipasok oleh Subsistem Kediri (UP2B Jawa Timur). 4.Pengaturan pemeliharaan saat beban rendah/hari libur dengan looping 3 IBT Pedan Mitigasi serta pengaturan konfigurasi</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10920,17 +9897,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Berpotensi padam sebesar 799 MW apabila terjadi gangguan pada 2 IBT (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Berpotensi padam sebesar 799 MW apabila terjadi gangguan pada 2 IBT (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 3,4 Pedan dengan total target sebesar 533MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 2.Pengoperasian PLTU Pacitan 1 unit sebesar 280 MW memasok Subsistem Pedan 3,4. 3.Pengaturanpemeli haraansaatbebanr endah/hariliburde nganlooping 3 IBT Pedansertapengat urankonfigurasi. 4.Terdapat DS Island Subsistem Pedan 3,4 (PLTU Pacitan)</t>
+          <t>1.Sudah terpasang OLS IBT 3,4 Pedan dengan total target sebesar 533 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 2.Pengoperasian PLTU Pacitan 1 unit sebesar 280 MW memasok Subsistem Pedan 3,4. 3.Pengaturanpemeli haraansaatbebanr endah/hariliburde nganlooping 3 IBT Pedansertapengat urankonfigurasi. 4.Terdapat DS Island Subsistem Pedan 3,4 (PLTU Pacitan)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3.Percepatan pembangunan SUTT 150 kV Pedan-Solobaru (RUPTL 2025-2034, COD 2027). 4.Usulan pemasangan DS OLS SUTT 150 kV Kebumen-Gombong. Rencana COD 2026. 5.Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025- 2034, COD 2028). 6.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028). 7.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: Usulan / Solusi 8.Rekonduktoring SUTT 150 kV Purworejo- Wates menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025- 2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
+          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3.Percepatan pembangunan SUTT 150 kV Pedan-Solobaru (RUPTL 2025-2034, COD 2027). 4.Usulan pemasangan DS OLS SUTT 150 kV Kebumen-Gombong. Rencana COD 2026. 5.Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025- 2034, COD 2028). 6.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028). 7.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: Usulan / Solusi 8.Rekonduktoring SUTT 150 kV Purworejo- Wates menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025- 2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -10955,7 +9932,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Berpotensi padam meluas apabila terjadi gangguan pada 2 IBT (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Berpotensi padam meluas apabila terjadi gangguan pada 2 IBT (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -10965,7 +9942,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3.Percepatan pembangunan SUTT 150 kV Pedan-SoloBaru (RUPTL 2025-2034, COD 2027). 4.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026 ). 5.Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025- 2034, COD 2028). 6.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028). 7.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: Usulan / Solusi 8.Rekonduktoring SUTT 150 kV Purworejo- Wates menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025- 2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
+          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3.Percepatan pembangunan SUTT 150 kV Pedan-SoloBaru (RUPTL 2025-2034, COD 2027). 4.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026 ). 5.Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025- 2034, COD 2028). 6.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028). 7.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: Usulan / Solusi 8.Rekonduktoring SUTT 150 kV Purworejo- Wates menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025- 2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -10990,17 +9967,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,2 Kesugihandengan total target sebesar 446MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 2.Pengoperasian PLTA Mrica. 3.Pergeseran beban GI ke subsistem lain</t>
+          <t>1.Sudah terpasang OLS IBT 1,2 Kesugihan dengan total target sebesar 446 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 2.Pengoperasian PLTA Mrica. 3.Pergeseran beban GI ke subsistem lain</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Jangka Menengah: 1.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025-2034, COD 2028). 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028). 3.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
+          <t>Jangka Menengah: 1.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025-2034, COD 2028). 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028). 3.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -11025,17 +10002,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Berpotensi padam sebesar 525 MW apabila terjadi gangguan pada 2 IBT (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Berpotensi padam sebesar 525 MW apabila terjadi gangguan pada 2 IBT (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.Rekonfigurasi jaringan di GI Kebasen ke Subsistem Mandirancan. 2.Sudah terpasang OLS IBT Pemalang 1,2sebesar451M W (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 3.Pengaturan pemeliharaan saat beban rendah/hari libur</t>
+          <t>1.Rekonfigurasi jaringan di GI Kebasen ke Subsistem Mandirancan. 2.Sudah terpasang OLS IBT Pemalang 1,2 sebesar451M W (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 3.Pengaturan pemeliharaan saat beban rendah/hari libur</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan extension IBT ke-3&amp;4 Pemalang/New Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang.SesuaiRUPTL 2025-2034, COD 2027). 2.Pembangunan SUTT 150 kV Dieng -New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027</t>
+          <t>Jangka Pendek: 1.Pembangunan extension IBT ke-3&amp;4 Pemalang/New Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang. SesuaiRUPTL 2025-2034, COD 2027). 2.Pembangunan SUTT 150 kV Dieng - New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -11095,7 +10072,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Terjadi overloadpada IBT 3 Ungaransaat terjadi gangguan SUTET Ungaran-Boyolali</t>
+          <t>Terjadi overloadpada IBT 3 Ungaran saat terjadi gangguan SUTET Ungaran-Boyolali</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11130,17 +10107,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.Overload pada IBT apabila trip 1 IBT sehingga keandalan berkurang dan harus dipasang OLS. 2.Kesulitan dalam pemeliharaan Busbar 150 kV. 3.Fleksibilitas operasi dan keandalan berkurang</t>
+          <t>1. Overload pada IBT apabila trip 1 IBT sehingga keandalan berkurang dan harus dipasang OLS. 2. Kesulitan dalam pemeliharaan Busbar 150 kV. 3. Fleksibilitas operasi dan keandalan berkurang</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Krian 1,2 - Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pengoperasikan Pembangkitan Gresik sesuai batasanya. 3.Pekerjaan dilakukan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Krian 1,2 - Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar 997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pengoperasikan Pembangkitan Gresik sesuai batasanya. 3. Pekerjaan dilakukan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing-masing subsistem 2. Pembangunan SUTET 500 kV Krian- Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun 2027, MundurCOD 2028). Update : sudah terkontrak 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. 4. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing-masing subsistem 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, CODTahun 2027, Mundur COD 2028). Update : sudah terkontrak 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. 4. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -11165,17 +10142,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.Overload pada IBT apabila trip 1 IBT. 2.Kesulitan saat melakukan pemeliharaan</t>
+          <t>1. Overload pada IBT apabila trip 1 IBT. 2. Kesulitan saat melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Krian 1,2 - Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan dilakukanpada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Krian 1,2 - Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar 997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note : Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing-masing subsistem 2.Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028. Update : sudah terkontrak. 3.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5.Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW di Guluk-guluk. Berdasaerkan RUPTL 2025-2034 COD Base tahun 2029 Usulan / Solusi 6.Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 7.Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 8.Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note : Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing-masing subsistem 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028. Update : sudah terkontrak. 3. PenambahanBattery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW di Guluk-guluk. Berdasaerkan RUPTL 2025-2034 COD Base tahun 2029 Usulan / Solusi 6. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 7. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 8. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -11200,17 +10177,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.Overload pada IBT apabila trip 1 IBT sehingga keandalan berkurang. 2.Bus Section Krian belum bisa dioperasikan sesuaifungsinya. 3.Kesulitan dalam melakukan pemeliharaan Busbar 150 kV</t>
+          <t>1. Overload pada IBT apabila trip 1 IBT sehingga keandalan berkurang. 2. Bus Section Krian belum bisa dioperasikan sesuaifungsinya. 3. Kesulitan dalam melakukan pemeliharaan Busbar 150 kV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Krian 3,4,5,6dengan tahapan 1-3 dan total target sebesar 578 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Krian 3,4,5,6 dengan tahapan 1-3 dan total target sebesar 578 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Percepatan Rekonfigurasi dan Rerouting SUTT 150 kVBanaran- MojoagungmenjadiSU TT 150 kV Kediri- Mojoagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025). Update : proses pengadaan 2.Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note: Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing-masing subsistem 3.Pembangunan SUTET 500 kV Krian - Waru. Usulan / Solusi (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028. 4.Percepatan pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. JangkaPanjang: 5.Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2032)</t>
+          <t>Jangka Pendek : 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kV Banaran- Mojoagung menjadi SU TT 150 kV Kediri- Mojoagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025). Update : proses pengadaan 2. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note: Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing-masing subsistem 3. Pembangunan SUTET 500 kV Krian - Waru. Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028. 4. Percepatan pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. Jangka Panjang: 5. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
         </is>
       </c>
     </row>
@@ -11235,17 +10212,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam beban pada Subsistem tersebut. 2.Kesulitan dalam melakukan pemeliharaan IBT apabila bersamaan dengan outage pembangkit PLTU Tanjung Awar- awar 2 unit</t>
+          <t>1. Berpotensi padam beban pada Subsistem tersebut. 2. Kesulitan dalam melakukan pemeliharaan IBT apabila bersamaan dengan outage pembangkit PLTU Tanjung Awar- awar 2 unit</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Ngimbang dengan total target sebesar485 MW. (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan dilakukan saat beban rendah atau menyesuaikan kondisi pembangkitan</t>
+          <t>1. Sudah terpasang OLS IBT Ngimbang dengan total target sebesar 485 MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah atau menyesuaikan kondisi pembangkitan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan PLTS 150 kV - 50 MW di Bojonegoro (Berdasarkan RUPTL 2025 - 2034, COD Tahun2026). 2.Penambahan Ext. IBT #3 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025) informasi terupdate COD Juli 2026. Update : sudah terkontrak. Note: penambahan 2 diameter, 4CB COD Tahun 2026) 3.Pembangunan GITET 500 kV Tanjung Awar awar dan Line Bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Update : Proses Survei dan pengukuran. 4.Penambahan Ext. IBT #4 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah: Usulan / Solusi 5.Pembangunan PLTB 150 kV dengan Total 200 MW Tahap I di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang: 6.Pembangunan PLTB 150 kV dengan Total 100 MW Tahap II di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
+          <t>Jangka Pendek: 1. Pembangunan PLTS 150 kV - 50 MW di Bojonegoro (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Ext. IBT #3 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025) informasi terupdate COD Juli 2026. Update : sudah terkontrak. Note: penambahan 2 diameter, 4CB COD Tahun 2026) 3. Pembangunan GITET 500 kV Tanjung Awar awar dan Line Bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Update : Proses Survei dan pengukuran. 4. Penambahan Ext. IBT #4 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah: Usulan / Solusi 5. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap I di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang: 6. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap II di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
         </is>
       </c>
     </row>
@@ -11270,17 +10247,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam beban pada Subsistem tersebut. 2.Kesulitan dalam melakukan pemeliharaan IBT</t>
+          <t>1. Berpotensi padam beban pada Subsistem tersebut. 2. Kesulitan dalam melakukan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Kediri 1,2 dengan total target sebesar336MW. ( Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan IBT tidak boleh berbarengan dengan pekerjaan di SS Surabaya barat dan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Kediri 1,2 dengan total target sebesar 336MW. ( Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan IBT tidak boleh berbarengan dengan pekerjaan di SS Surabaya barat dan saat beban rendah</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2027). Jangka Menengah: 2.Pembangunan PLTB 150KV Total 200 MW Tahap I di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang: 3.Pembangunan PLTB 150KV Total 200 MW Tahap II di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 4.Pembangunan PLTP Gunung Pandandan line bay terkait. (Berdasarkan RUPTL 2025-2034, CODtahun 2033)</t>
+          <t>Jangka Pendek: 1. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah: 2. Pembangunan PLTB 150KV Total 200 MW Tahap I di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang: 3. Pembangunan PLTB 150KV Total 200 MW Tahap II di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 4. Pembangunan PLTP Gunung Pandandan line bay terkait. (Berdasarkan RUPTL 2025 -2034, CODtahun 2033)</t>
         </is>
       </c>
     </row>
@@ -11310,12 +10287,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.Pengaturan rekonfigurasi di subsistem Kediri 1,2 dan Kediri 3,4 saat outage. 2.Sudah terpasang OLS IBT Kediri 3,4 dengan total target sebesar 369 MW (Berdasarkan Deklarasi ROB Mei 2026). Mitigasi 3.Pekerjaan dilakukan saat beban rendah dan menyesuaikan kondisi pembangkitan PLTU Pacitan</t>
+          <t>1. Pengaturan rekonfigurasi di subsistem Kediri 1,2 dan Kediri 3,4 saat outage. 2. Sudah terpasang OLS IBT Kediri 3,4 dengan total target sebesar 369 MW (Berdasarkan Deklarasi ROB Mei 2026). Mitigasi 3. Pekerjaan dilakukan saat beban rendah dan menyesuaikan kondisi pembangkitan PLTU Pacitan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan PLTS 150KV - 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Usulan / Solusi Tahun 2026). informasi terupdate COD Desember 2027 Jangka Menengah: 3.Pembangunan PLTP Ngebel/PLTP Gunung Wilis dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang: 4.Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025-2034, COD diluar RUPTL). 5.Pembangunan PLTB 150KV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek: 1. Pembangunan PLTS 150KV - 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Usulan / Solusi Tahun 2026). informasi terupdate COD Desember 2027 Jangka Menengah: 3. Pembangunan PLTP Ngebel/PLTP Gunung Wilis dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang: 4. Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD diluar RUPTL). 5. Pembangunan PLTB 150KV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -11340,17 +10317,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.Overload jika terjadi trip salah satu IBT. 2.Kesulitan dalam melakukan pemeliharaan IBT</t>
+          <t>1. Overload jika terjadi trip salah satu IBT. 2. Kesulitan dalam melakukan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Grati dengan total target sebesar 665 MW (Berdasarkan Deklarasi ROB Mei Tahun 2026). 2.Pengoperasian Block 2 Grati (add on). 3.Pekerjaan dilaksanakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Grati dengan total target sebesar 665 MW (Berdasarkan Deklarasi ROB Mei Tahun 2026). 2. Pengoperasian Block 2 Grati (add on). 3. Pekerjaan dilaksanakan saat beban rendah</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2026 (informasi terupdate COD Juni 2026). 2.Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3.Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Update : proses pengadaan. 4.Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL Usulan / Solusi 2025 - 2034, COD Tahun 2026). 5.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). JangkaMenengah: 6.Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 7.Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 8.Pembangunan PLTB 150KV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 9.Pembangunan PLTB 150KV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2026 (informasi terupdate COD Juni 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Update : proses pengadaan. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL Usulan / Solusi 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menengah: 6.Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 7. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 8. Pembangunan PLTB 150KV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 9. Pembangunan PLTB 150KV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -11375,17 +10352,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.Overload di IBT-2 Paiton jika dilakukan looping dengan Subsistem Grati. 2.Kesulitan dalam melakukan pemeliharaan IBT</t>
+          <t>1. Overload di IBT-2 Paiton jika dilakukan looping dengan Subsistem Grati. 2. Kesulitan dalam melakukan pemeliharaan IBT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 2 Paiton dengan total target sebesar 178MW ((berdasarkan Deklasarasi ROB Mei2026)). 2.Sudah terpasang Adaptive Defense Scheme (ADS) Paiton-Bali. 3.Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
+          <t>1. Sudah terpasang OLS IBT 2 Paiton dengan total target sebesar 178 MW ((berdasarkan Deklasarasi ROB Mei 2026)). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton -Bali. 3. Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Penambahan IBT-4 di GITET Paiton.(hasil dari action Tracker dipilih IBT - 4 Paiton Untuk Solusi Shorterm) (Berdasarkan RUPTL 2025-2034, COD Base Tahun 2026). 2.Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Usulan / Solusi 3.Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Update : proses pengadaan. 4.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5.Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton-Situbondo, COD Tahun2026. 6.Pembangunan PLTS 150 kV dengan total 50 MW di Paiton (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. Jangka Menengah: 7. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 8. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Usulan / Solusi Update : proses pengadaan. 9. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun2026). Jangka Panjang: 10. Pembangunan PLTP Iyang Argopurodan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL). 11. Pembangunan PLTS Jawa Timur di Probolinggo (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
+          <t>Jangka Pendek : 1. Penambahan IBT-4 di GITET Paiton. (hasil dari action Tracker dipilih IBT - 4 Paiton Untuk Solusi Shorterm) (Berdasarkan RUPTL 2025 -2034, COD Base Tahun 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Usulan / Solusi 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Update : proses pengadaan. 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton-Situbondo, COD Tahun 2026. 6. Pembangunan PLTS 150 kV dengan total 50 MW di Paiton (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. Jangka Menengah: 7. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 8. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Usulan / Solusi Update : proses pengadaan. 9. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Panjang: 10. Pembangunan PLTP Iyang Argopurodan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL). 11. Pembangunan PLTS Jawa Timur di Probolinggo (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -11415,12 +10392,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,3Paiton dengan total target sebesar 775 MW (berdasarkan Deklarasi ROB Mei 2026). 2.Sudah terpasang Adaptive Defense Scheme (ADS) Paiton-Bali. 3.Dioperasikan Pararel 3 IBT di GI Paiton1 Busbar, Per 10 Februari 2025</t>
+          <t>1. Sudah terpasang OLS IBT 1,3 Paiton dengan total target sebesar 775 MW (berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton -Bali. 3. Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Penambahan IBT-4 di GITET Paiton.(hasil dari action Tracker dipilih IBT - 4 Paiton Untuk Solusi Shorterm) (Berdasarkan RUPTL 2025-2034, COD Base Tahun 2026). 2.Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3.Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Update : proses pengadaan). 4.Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol</t>
+          <t>Jangka Pendek : 1. Penambahan IBT-4 di GITET Paiton. (hasil dari action Tracker dipilih IBT - 4 Paiton Untuk Solusi Shorterm) (Berdasarkan RUPTL 2025 -2034, COD Base Tahun 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. Update : proses pengadaan). 4. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol</t>
         </is>
       </c>
     </row>
